--- a/materials/asmr_template.xlsx
+++ b/materials/asmr_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://univpm-my.sharepoint.com/personal/s1116344_pm_univpm_it/Documents/PhD/ASMR/Use_cases/ASMR_guidelines/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\ASMR\materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="356" documentId="8_{3759D2ED-E884-48E0-9DE7-EE8AE53D82EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{747F553F-1EDC-44C8-82C6-328A6E80ED07}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1734BC3-881A-447A-B561-C76A8BB71ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="16" xr2:uid="{AFBFBA82-9AEE-4DB2-BCE9-4DEFE9217D81}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="12" xr2:uid="{AFBFBA82-9AEE-4DB2-BCE9-4DEFE9217D81}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="25" r:id="rId1"/>
